--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260316_203032.xlsx
@@ -4802,7 +4802,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
